--- a/content/Assignments/02-coursework-part-b/staff/part-b-marking-grid-template.xlsx
+++ b/content/Assignments/02-coursework-part-b/staff/part-b-marking-grid-template.xlsx
@@ -696,7 +696,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enter 'NS' in the Total column for non-submissions. See ../marking/ for the rubric-to-evidence map and comment bank.</t>
+          <t>Enter 'NS' in the Total column for non-submissions. See rubric-to-evidence-map.md and feedback-comment-bank.md in this folder.</t>
         </is>
       </c>
     </row>
